--- a/data/trans_dic/P22$mutaSS-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P22$mutaSS-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Mutualidad de Estado (Seguridad Social)</t>
+          <t>Población que, al menos, es beneficiaria de mutualidades del Estado (Seguridad Social) (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,48</t>
+          <t>0,89; 2,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,3</t>
+          <t>0,29; 1,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,14</t>
+          <t>0,53; 2,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,1</t>
+          <t>1,46; 3,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,09</t>
+          <t>0,69; 1,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,12</t>
+          <t>0,12; 1,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,62</t>
+          <t>0,05; 0,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,58</t>
+          <t>1,36; 2,48</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,51</t>
+          <t>0,61; 1,41</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,19</t>
+          <t>0,38; 1,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,49</t>
+          <t>0,09; 0,48</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 3,66</t>
+          <t>2,04; 3,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,16</t>
+          <t>1,72; 3,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,46</t>
+          <t>1,27; 2,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,46</t>
+          <t>1,64; 3,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,22</t>
+          <t>2,39; 4,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,69</t>
+          <t>1,36; 2,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,3</t>
+          <t>0,46; 1,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,2</t>
+          <t>0,55; 1,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 3,68</t>
+          <t>2,39; 3,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,68</t>
+          <t>1,74; 2,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 1,77</t>
+          <t>1,03; 1,75</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,17</t>
+          <t>1,23; 2,17</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,72; 12,95</t>
+          <t>7,5; 12,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,23; 10,86</t>
+          <t>5,45; 10,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,91; 7,86</t>
+          <t>3,93; 7,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 7,08</t>
+          <t>3,58; 7,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,67; 9,53</t>
+          <t>4,94; 9,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 7,81</t>
+          <t>3,31; 8,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 6,9</t>
+          <t>2,99; 6,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,59; 7,47</t>
+          <t>4,65; 7,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,91; 10,3</t>
+          <t>7,06; 10,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,92; 8,56</t>
+          <t>4,77; 8,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,91; 6,68</t>
+          <t>3,94; 6,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,52; 6,67</t>
+          <t>4,53; 6,72</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,97; 4,3</t>
+          <t>2,98; 4,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,27</t>
+          <t>2,05; 3,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 2,88</t>
+          <t>1,8; 2,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,31</t>
+          <t>1,96; 3,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 4,04</t>
+          <t>2,75; 4,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,68</t>
+          <t>1,62; 2,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,71</t>
+          <t>0,94; 1,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,03</t>
+          <t>1,25; 2,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,01; 3,99</t>
+          <t>3,03; 3,96</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 2,78</t>
+          <t>1,98; 2,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,14</t>
+          <t>1,47; 2,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,53</t>
+          <t>1,74; 2,56</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Mutualidad de Estado (Seguridad Social)</t>
+          <t>Población que, al menos, es beneficiaria de mutualidades del Estado (Seguridad Social) (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9358; 25563</t>
+          <t>9163; 25649</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2778; 12709</t>
+          <t>2828; 12739</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3836; 16143</t>
+          <t>3995; 16491</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4344</t>
+          <t>0; 3987</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19219; 40696</t>
+          <t>19212; 40675</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9325; 27952</t>
+          <t>9249; 25893</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1098; 11049</t>
+          <t>1165; 11006</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>387; 4637</t>
+          <t>382; 4385</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32266; 60536</t>
+          <t>31933; 58069</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14234; 34819</t>
+          <t>14133; 32614</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7014; 20684</t>
+          <t>6549; 20651</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1088; 6223</t>
+          <t>1146; 6101</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33662; 61809</t>
+          <t>34475; 62144</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35139; 61991</t>
+          <t>33795; 62605</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26448; 51073</t>
+          <t>26343; 52057</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35914; 79336</t>
+          <t>37502; 77894</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38748; 66905</t>
+          <t>37902; 66542</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23318; 47327</t>
+          <t>23868; 46196</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8982; 25870</t>
+          <t>9052; 25905</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12351; 26897</t>
+          <t>12342; 27530</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>79912; 120425</t>
+          <t>78248; 117370</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62574; 99583</t>
+          <t>64799; 102568</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41058; 72038</t>
+          <t>41890; 70904</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>55432; 98269</t>
+          <t>55848; 98120</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>42584; 71435</t>
+          <t>41377; 70690</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25168; 52280</t>
+          <t>26242; 51362</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21356; 42921</t>
+          <t>21473; 43318</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24049; 45770</t>
+          <t>23141; 46301</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22259; 45425</t>
+          <t>23520; 47334</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14468; 35809</t>
+          <t>15164; 36970</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17396; 37903</t>
+          <t>16404; 38077</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30300; 49336</t>
+          <t>30742; 49922</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>71014; 105887</t>
+          <t>72540; 109226</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46248; 80471</t>
+          <t>44867; 80324</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42782; 73201</t>
+          <t>43099; 72827</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>59042; 87195</t>
+          <t>59159; 87850</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>97240; 140671</t>
+          <t>97585; 139614</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73683; 111869</t>
+          <t>70165; 112993</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60001; 96994</t>
+          <t>60756; 96829</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>70676; 114113</t>
+          <t>67558; 116083</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>94062; 136296</t>
+          <t>92763; 135492</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>58675; 95106</t>
+          <t>57410; 94810</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32403; 60429</t>
+          <t>33304; 61171</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>46593; 74214</t>
+          <t>45807; 73159</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>200172; 265303</t>
+          <t>201647; 263294</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>139581; 193519</t>
+          <t>138251; 191725</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>100213; 147395</t>
+          <t>101630; 146355</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>124223; 180031</t>
+          <t>123896; 181749</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$mutaSS-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P22$mutaSS-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,49</t>
+          <t>0,92; 2,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,31</t>
+          <t>0,21; 1,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,19</t>
+          <t>0,41; 2,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,09</t>
+          <t>1,48; 3,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,94</t>
+          <t>0,77; 1,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,11</t>
+          <t>0,11; 1,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,58</t>
+          <t>0,08; 0,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,48</t>
+          <t>1,38; 2,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,41</t>
+          <t>0,61; 1,47</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,18</t>
+          <t>0,37; 1,25</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,48</t>
+          <t>0,08; 0,53</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -857,52 +857,52 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 3,68</t>
+          <t>2,04; 3,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,19</t>
+          <t>1,75; 3,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,51</t>
+          <t>1,3; 2,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,4</t>
+          <t>1,83; 3,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,19</t>
+          <t>2,42; 4,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,63</t>
+          <t>1,33; 2,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,3</t>
+          <t>0,46; 1,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,23</t>
+          <t>0,66; 1,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 3,58</t>
+          <t>2,36; 3,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,76</t>
+          <t>1,73; 2,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,17</t>
+          <t>1,33; 2,18</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,5; 12,82</t>
+          <t>7,63; 12,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,45; 10,67</t>
+          <t>5,31; 10,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,93; 7,93</t>
+          <t>3,98; 7,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,58; 7,16</t>
+          <t>3,46; 6,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,94; 9,94</t>
+          <t>4,94; 9,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 8,06</t>
+          <t>3,35; 8,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,99; 6,93</t>
+          <t>3,0; 6,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,56</t>
+          <t>4,47; 7,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,06; 10,63</t>
+          <t>6,92; 10,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,77; 8,55</t>
+          <t>4,94; 8,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,94; 6,65</t>
+          <t>3,92; 6,62</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,53; 6,72</t>
+          <t>4,26; 6,4</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,98; 4,27</t>
+          <t>2,95; 4,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,31</t>
+          <t>2,08; 3,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,87</t>
+          <t>1,78; 2,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,36</t>
+          <t>2,11; 3,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,75; 4,01</t>
+          <t>2,74; 3,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,67</t>
+          <t>1,64; 2,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 1,73</t>
+          <t>0,96; 1,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,0</t>
+          <t>1,42; 2,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,03; 3,96</t>
+          <t>2,98; 3,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 2,75</t>
+          <t>1,98; 2,76</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,12</t>
+          <t>1,49; 2,15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,56</t>
+          <t>1,86; 2,5</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>3277</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9163; 25649</t>
+          <t>9426; 24949</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2828; 12739</t>
+          <t>2049; 11733</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3995; 16491</t>
+          <t>3125; 15310</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3987</t>
+          <t>0; 4890</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19212; 40675</t>
+          <t>19423; 41384</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9249; 25893</t>
+          <t>10261; 26489</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1165; 11006</t>
+          <t>1092; 10307</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>382; 4385</t>
+          <t>671; 5860</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31933; 58069</t>
+          <t>32351; 59071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14133; 32614</t>
+          <t>14188; 33970</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6549; 20651</t>
+          <t>6452; 21829</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1146; 6101</t>
+          <t>1088; 7472</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56715</t>
+          <t>55884</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>19139</t>
+          <t>20338</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>75854</t>
+          <t>76222</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34475; 62144</t>
+          <t>34487; 61772</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33795; 62605</t>
+          <t>34258; 61954</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26343; 52057</t>
+          <t>27035; 51388</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37502; 77894</t>
+          <t>40883; 72795</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37902; 66542</t>
+          <t>38416; 67770</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23868; 46196</t>
+          <t>23386; 46933</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9052; 25905</t>
+          <t>9132; 26309</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12342; 27530</t>
+          <t>14275; 28065</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>78248; 117370</t>
+          <t>77460; 118471</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>64799; 102568</t>
+          <t>64463; 99940</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41890; 70904</t>
+          <t>41914; 70942</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>55848; 98120</t>
+          <t>58729; 95827</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33329</t>
+          <t>35492</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39029</t>
+          <t>41501</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>72358</t>
+          <t>76993</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>41377; 70690</t>
+          <t>42064; 70842</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26242; 51362</t>
+          <t>25569; 51523</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21473; 43318</t>
+          <t>21719; 42916</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23141; 46301</t>
+          <t>24631; 48503</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23520; 47334</t>
+          <t>23556; 46925</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15164; 36970</t>
+          <t>15376; 37478</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16404; 38077</t>
+          <t>16486; 38186</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30742; 49922</t>
+          <t>32823; 52665</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>72540; 109226</t>
+          <t>71102; 107636</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44867; 80324</t>
+          <t>46458; 78364</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>43099; 72827</t>
+          <t>42937; 72493</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>59159; 87850</t>
+          <t>61685; 92627</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>91149</t>
+          <t>92585</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>60018</t>
+          <t>63906</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>151167</t>
+          <t>156491</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>97585; 139614</t>
+          <t>96485; 139565</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>70165; 112993</t>
+          <t>71275; 110524</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60756; 96829</t>
+          <t>59934; 97362</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>67558; 116083</t>
+          <t>74262; 113984</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>92763; 135492</t>
+          <t>92490; 134696</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>57410; 94810</t>
+          <t>58212; 93881</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33304; 61171</t>
+          <t>33767; 61264</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>45807; 73159</t>
+          <t>52981; 76241</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>201647; 263294</t>
+          <t>198013; 261137</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>138251; 191725</t>
+          <t>138230; 192658</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>101630; 146355</t>
+          <t>102607; 148335</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>123896; 181749</t>
+          <t>134859; 181497</t>
         </is>
       </c>
     </row>
